--- a/verificables revisión sistemática/S16_excluidos_tras_leer_el_texto_completo.xlsx
+++ b/verificables revisión sistemática/S16_excluidos_tras_leer_el_texto_completo.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$H$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$H$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -529,7 +529,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>22 filas de datos</t>
+          <t>26 filas de datos</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -722,32 +722,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>EST-017</t>
+          <t>EST-092</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>INT</t>
+          <t>IDI</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>La intervencion no es un bacteriofago (endolisina u otro derivado)</t>
+          <t>Informe no redactado en ingles ni en espanol (criterio de idioma, enmienda 2026-08-11)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Inducen-Res(R): solucion oral "imprinted with the induction signatures" para inducir los fagos nativos del propio paciente; no se administra ningun fago. Ademas sin diagnostico confirmado.</t>
+          <t>Cuerpo del articulo en ruso: 94,1 % de caracteres cirilicos medidos sobre la pagina del editor (mediasphera.ru) SIN traduccion automatica. Lo latino es el resumen en ingles, las palabras clave y las referencias. NO existe version inglesa: /en/ devuelve 404, ?lang=en devuelve la misma pagina cirilica y /downloads/en/ no entrega PDF. El registro ya lo tenia como idioma_declarado=rus y aun asi ADMITIDO, porque el detector midio el resumen y no el cuerpo.</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>despite not having a primary diagnosis of the specific types of infections involved ... could be anticipated</t>
+          <t>Pirogov Russian Journal of Surgery / Хирургия. Журнал им. Н.И. Пирогова -- cuerpo integro en ruso</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Successful Treatment of a Patient With Chronic Bronchiectasis Using an Induced Native Phage Cocktail: A Case Report.</t>
+          <t>Phage therapy analysis of effectiveness in comorbid patients with wounds and surgical infections of various etiology based on the results of a compara</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -764,32 +764,32 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>EST-199</t>
+          <t>EST-103</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>INT</t>
+          <t>IDI</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>La intervencion no es un bacteriofago (endolisina u otro derivado)</t>
+          <t>Informe no redactado en ingles ni en espanol (criterio de idioma, enmienda 2026-08-11)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Endolisina de fago (79 menciones de lysin), no un bacteriofago.</t>
+          <t>Cuerpo del articulo en ruso: 77,9 % de caracteres cirilicos medidos sobre la pagina del editor (mediasphera.ru) SIN traduccion automatica. Lo latino es el resumen en ingles, las palabras clave y las referencias. NO existe version inglesa: /en/ devuelve 404, ?lang=en devuelve la misma pagina cirilica y /downloads/en/ no entrega PDF. El registro ya lo tenia como idioma_declarado=rus y aun asi ADMITIDO, porque el detector midio el resumen y no el cuerpo.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Successful use of a phage endolysin for treatment of chronic pelvic pain syndrome</t>
+          <t>Pirogov Russian Journal of Surgery / Хирургия. Журнал им. Н.И. Пирогова -- cuerpo integro en ruso</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Successful use of a phage endolysin for treatment of chronic pelvic pain syndrome/chronic bacterial prostatitis</t>
+          <t>Phage therapy of purulent wounds: comparative clinical cytomorphological and microbiological analysis of effectiveness; [Фаготерапиягнойныхран:сравнит</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -806,32 +806,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>EST-020</t>
+          <t>EST-147</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LAB</t>
+          <t>IDI</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Trabajo de laboratorio, preclinico o de modelizacion; sin pacientes tratados</t>
+          <t>Informe no redactado en ingles ni en espanol (criterio de idioma, enmienda 2026-08-11)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Modelo murino de neumonia asociada a ventilacion.</t>
+          <t>Cuerpo del articulo en ruso: 91,0 % de caracteres cirilicos medidos sobre la pagina del editor (mediasphera.ru) SIN traduccion automatica. Lo latino es el resumen en ingles, las palabras clave y las referencias. NO existe version inglesa: /en/ devuelve 404, ?lang=en devuelve la misma pagina cirilica y /downloads/en/ no entrega PDF. El registro ya lo tenia como idioma_declarado=rus y aun asi ADMITIDO, porque el detector midio el resumen y no el cuerpo.</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>C57BL/6J mice were ventilated with high tidal volume ... in a murine model</t>
+          <t>Pirogov Russian Journal of Surgery / Хирургия. Журнал им. Н.И. Пирогова -- cuerpo integro en ruso</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Adjunctive phage therapy improves antibiotic treatment of ventilator-associated-pneumonia with Pseudomonas aeruginosa.</t>
+          <t>Complex surgical treatment of recurrent post-injection abscess in a patient with systemic autoimmune disease; [Комплексное хирургическое лечение рецид</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -848,32 +848,32 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>EST-041</t>
+          <t>EST-219</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LAB</t>
+          <t>IDI</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Trabajo de laboratorio, preclinico o de modelizacion; sin pacientes tratados</t>
+          <t>Informe no redactado en ingles ni en espanol (criterio de idioma, enmienda 2026-08-11)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Articulo de metodos: canal de preparacion de fagos en el laboratorio.</t>
+          <t>Cuerpo del articulo en ruso: 93,0 % de caracteres cirilicos medidos sobre la pagina del editor (mediasphera.ru) SIN traduccion automatica. Lo latino es el resumen en ingles, las palabras clave y las referencias. NO existe version inglesa: /en/ devuelve 404, ?lang=en devuelve la misma pagina cirilica y /downloads/en/ no entrega PDF. El registro ya lo tenia como idioma_declarado=rus y aun asi ADMITIDO, porque el detector midio el resumen y no el cuerpo. ADEMAS falla por poblacion: 111 pacientes con infecciones purulentas de la mano, patogenos predominantes Staphylococcus y Streptococcus; P. aeruginosa solo aparece en la composicion del piobacteriofago.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>we present an efficient modular pipeline for individualized, timely, safe and high-quality phage solutions</t>
+          <t>Pirogov Russian Journal of Surgery / Хирургия. Журнал им. Н.И. Пирогова -- cuerpo integro en ruso</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Optimized preparation pipeline for emergency phage therapy against Pseudomonas aeruginosa at Yale University.</t>
+          <t>Bacteriophages in complex treatment of septic diseases of the hand; [Использование лекарственных препаратов бактериофагов в комплексном лечении гнойны</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -890,32 +890,32 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>EST-093</t>
+          <t>EST-017</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LAB</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Trabajo de laboratorio, preclinico o de modelizacion; sin pacientes tratados</t>
+          <t>La intervencion no es un bacteriofago (endolisina u otro derivado)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Modelo in vitro: time-kill de 24 h y hollow fibre de 7 dias.</t>
+          <t>Inducen-Res(R): solucion oral "imprinted with the induction signatures" para inducir los fagos nativos del propio paciente; no se administra ningun fago. Ademas sin diagnostico confirmado.</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>evaluated as mono- or dual-phage therapy against a clinical Pseudomonas aeruginosa in 24 h static time kills and in 7-day hollow fibre infection model</t>
+          <t>despite not having a primary diagnosis of the specific types of infections involved ... could be anticipated</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Pharmacodynamic individualization of phage therapy against a KPC-5-producing Pseudomonas aeruginosa.</t>
+          <t>Successful Treatment of a Patient With Chronic Bronchiectasis Using an Induced Native Phage Cocktail: A Case Report.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -932,32 +932,32 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>EST-037</t>
+          <t>EST-199</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>INT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No evalua fagoterapia en pacientes (encuesta, epidemiologia, prensa, otra terapia)</t>
+          <t>La intervencion no es un bacteriofago (endolisina u otro derivado)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Caso de shock septico por P. aeruginosa PDR donde el fago solo se menciona como opcion no disponible.</t>
+          <t>Endolisina de fago (79 menciones de lysin), no un bacteriofago.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Experimental therapies, including bacteriophages ... remain unavailable in most clinical settings</t>
+          <t>Successful use of a phage endolysin for treatment of chronic pelvic pain syndrome</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Pan-Resistant Pseudomonas aeruginosa Septic Shock in a Critically Ill Patient: A Case Report.</t>
+          <t>Successful use of a phage endolysin for treatment of chronic pelvic pain syndrome/chronic bacterial prostatitis</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -974,32 +974,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EST-185</t>
+          <t>EST-020</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>LAB</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>No evalua fagoterapia en pacientes (encuesta, epidemiologia, prensa, otra terapia)</t>
+          <t>Trabajo de laboratorio, preclinico o de modelizacion; sin pacientes tratados</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Articulo de cirugia reconstructiva de mediastinitis esternal. UNA mencion de fago en 43.000 caracteres, en una celda de tabla entre ocho antimicrobianos.</t>
+          <t>Modelo murino de neumonia asociada a ventilacion.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Avibactam, bacteriophage therapy, ceftazidime, colistin, meropenem, minocycline, piperacillin-tazobactam</t>
+          <t>C57BL/6J mice were ventilated with high tidal volume ... in a murine model</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>The management of sternal mediastinitis in heart and lung transplant patients: An 8-year experience and application of reconstructive algorithm</t>
+          <t>Adjunctive phage therapy improves antibiotic treatment of ventilator-associated-pneumonia with Pseudomonas aeruginosa.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1016,32 +1016,32 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EST-076</t>
+          <t>EST-041</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ORG</t>
+          <t>LAB</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Organismo distinto de P. aeruginosa, sin subgrupo separable</t>
+          <t>Trabajo de laboratorio, preclinico o de modelizacion; sin pacientes tratados</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Cero menciones. Artroplastias infectadas por Staphylococcus.</t>
+          <t>Articulo de metodos: canal de preparacion de fagos en el laboratorio.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Keywords: periprosthetic joint infections; Staphylococcus</t>
+          <t>we present an efficient modular pipeline for individualized, timely, safe and high-quality phage solutions</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Experience Using Adjuvant Bacteriophage Therapy for the Treatment of 10 Recalcitrant Periprosthetic Joint Infections: A Case Series.</t>
+          <t>Optimized preparation pipeline for emergency phage therapy against Pseudomonas aeruginosa at Yale University.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1058,28 +1058,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>EST-086</t>
+          <t>EST-093</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ORG</t>
+          <t>LAB</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Organismo distinto de P. aeruginosa, sin subgrupo separable</t>
+          <t>Trabajo de laboratorio, preclinico o de modelizacion; sin pacientes tratados</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Cepa de referencia ATCC 27853 usada para fabricar el coctel; pacientes de COVID-19.</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
+          <t>Modelo in vitro: time-kill de 24 h y hollow fibre de 7 dias.</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>evaluated as mono- or dual-phage therapy against a clinical Pseudomonas aeruginosa in 24 h static time kills and in 7-day hollow fibre infection model</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Inhalation phage therapy as a new approach to preventing secondary bacterial pneumonia in patients with moderate to severe COVID-19: A double-blind cl</t>
+          <t>Pharmacodynamic individualization of phage therapy against a KPC-5-producing Pseudomonas aeruginosa.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1096,32 +1100,32 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EST-101</t>
+          <t>EST-037</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ORG</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Organismo distinto de P. aeruginosa, sin subgrupo separable</t>
+          <t>No evalua fagoterapia en pacientes (encuesta, epidemiologia, prensa, otra terapia)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Ninos ventilados; los criterios excluian neumonia bacteriana; cultivos negativos.</t>
+          <t>Caso de shock septico por P. aeruginosa PDR donde el fago solo se menciona como opcion no disponible.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>excluded children with bacterial pneumonia</t>
+          <t>Experimental therapies, including bacteriophages ... remain unavailable in most clinical settings</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>The Efficacy of Inhaled Phage Cocktail to Prevent Ventilator-Associated Pneumonia in Children: A Double-Blind Clinical Trial</t>
+          <t>Pan-Resistant Pseudomonas aeruginosa Septic Shock in a Critically Ill Patient: A Case Report.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1138,32 +1142,32 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EST-126</t>
+          <t>EST-185</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ORG</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Organismo distinto de P. aeruginosa, sin subgrupo separable</t>
+          <t>No evalua fagoterapia en pacientes (encuesta, epidemiologia, prensa, otra terapia)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Etiqueta del piobacteriofago y una referencia. 212 ninos con amigdalitis aguda.</t>
+          <t>Articulo de cirugia reconstructiva de mediastinitis esternal. UNA mencion de fago en 43.000 caracteres, en una celda de tabla entre ocho antimicrobianos.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>the drug is recommended for use in treating ...</t>
+          <t>Avibactam, bacteriophage therapy, ceftazidime, colistin, meropenem, minocycline, piperacillin-tazobactam</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Application of bacteriophage therapy in the treatment of children with acute tonsillitis</t>
+          <t>The management of sternal mediastinitis in heart and lung transplant patients: An 8-year experience and application of reconstructive algorithm</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1180,7 +1184,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EST-130</t>
+          <t>EST-076</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1195,13 +1199,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Solo en la lista de referencias.</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
+          <t>Cero menciones. Artroplastias infectadas por Staphylococcus.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Keywords: periprosthetic joint infections; Staphylococcus</t>
+        </is>
+      </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Prolonged disease remission of the chronic immunological skin disorder hidradenitis suppurativa with adjunctive bacteriophage therapy.</t>
+          <t>Experience Using Adjuvant Bacteriophage Therapy for the Treatment of 10 Recalcitrant Periprosthetic Joint Infections: A Case Series.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1218,7 +1226,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EST-131</t>
+          <t>EST-086</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1233,13 +1241,13 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Solo en la lista de referencias, sus tres menciones.</t>
+          <t>Cepa de referencia ATCC 27853 usada para fabricar el coctel; pacientes de COVID-19.</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Results of TOR001: An open-label single patient study using targeted bacteriophage therapy for the treatment of a chronic urinary tract infection</t>
+          <t>Inhalation phage therapy as a new approach to preventing secondary bacterial pneumonia in patients with moderate to severe COVID-19: A double-blind cl</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1256,7 +1264,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EST-159</t>
+          <t>EST-101</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1271,13 +1279,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Espectro del coctel SniPha 360.</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
+          <t>Ninos ventilados; los criterios excluian neumonia bacteriana; cultivos negativos.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>excluded children with bacterial pneumonia</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bacteriophage-Enriched Galenic for Intrapericardial Ventricular Assist Device Infection</t>
+          <t>The Efficacy of Inhaled Phage Cocktail to Prevent Ventilator-Associated Pneumonia in Children: A Double-Blind Clinical Trial</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1294,7 +1306,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EST-178</t>
+          <t>EST-126</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1309,17 +1321,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Cero menciones en 22.705 caracteres, en ninguna grafia. Rinosinusitis aguda.</t>
+          <t>Etiqueta del piobacteriofago y una referencia. 212 ninos con amigdalitis aguda.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>USE OF POLYVALENT BACTERIOPHAGE ... IN PATIENTS WITH ARS</t>
+          <t>the drug is recommended for use in treating ...</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CLINICAL AND LABORATORY JUSTIFICATION FOR USE OF POLYVALENT BACTERIOPHAGE IN TECHNIQUE OF DELAYED PRESCRIBING OF ANTIBIOTICS IN PATIENTS WITH ARS.</t>
+          <t>Application of bacteriophage therapy in the treatment of children with acute tonsillitis</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1336,7 +1348,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>EST-207</t>
+          <t>EST-130</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1351,17 +1363,13 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>PDF correcto ya instalado (Europace 2020;22(4):597, DOI 10.1093/europace/euz319). Es un EP CASE EXPRESS de UNA pagina: varon de 41 anos, Marfan, infeccion de bolsillo de DAI e injerto vascular. CERO menciones de Pseudomonas o aeruginosa, y no nombra NINGUN microorganismo. La version completa del caso no esta en la revista, sino en una pagina de e-learning de la ESC. Fila extraida por un solo revisor.</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>A vacuum assisted closure treatment was initiated combined with antibiotics. Since no infection control was achieved, local application of a bacteriophage therapy was added.</t>
-        </is>
-      </c>
+          <t>Solo en la lista de referencias.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Successful bacteriophage treatment of infection involving cardiac implantable electronic device and aortic graft: a Trojan horse concept.</t>
+          <t>Prolonged disease remission of the chronic immunological skin disorder hidradenitis suppurativa with adjunctive bacteriophage therapy.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1378,7 +1386,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>EST-212</t>
+          <t>EST-131</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1393,17 +1401,13 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Espectro de SniPha 360; los cultivos dieron otra cosa.</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>microbiological analysis of intraoperative samples confirmed infection with Staphylococcus aureus and Proteus mirabilis</t>
-        </is>
-      </c>
+          <t>Solo en la lista de referencias, sus tres menciones.</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Local Treatment of Driveline Infection with Bacteriophages</t>
+          <t>Results of TOR001: An open-label single patient study using targeted bacteriophage therapy for the treatment of a chronic urinary tract infection</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1420,32 +1424,28 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>EST-035</t>
+          <t>EST-159</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PRO</t>
+          <t>ORG</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Protocolo de estudio: declara lo que se hara, sin resultados</t>
+          <t>Organismo distinto de P. aeruginosa, sin subgrupo separable</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>STUDY PROTOCOL en Trials (2022). 99 ocurrencias de "will be".</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Safety and microbiological activity of phage therapy in persons with cystic fibrosis</t>
-        </is>
-      </c>
+          <t>Espectro del coctel SniPha 360.</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Safety and microbiological activity of phage therapy in persons with cystic fibrosis colonized with Pseudomonas aeruginosa: study protocol for a phase</t>
+          <t>Bacteriophage-Enriched Galenic for Intrapericardial Ventricular Assist Device Infection</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1462,32 +1462,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>EST-052</t>
+          <t>EST-178</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>PRO</t>
+          <t>ORG</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Protocolo de estudio: declara lo que se hara, sin resultados</t>
+          <t>Organismo distinto de P. aeruginosa, sin subgrupo separable</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Documento de protocolo CYPHY, Yale, version 11. 223 ocurrencias de "will be".</t>
+          <t>Cero menciones en 22.705 caracteres, en ninguna grafia. Rinosinusitis aguda.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Protocol Number: 2000029160 November 29, 2022 Version 11</t>
+          <t>USE OF POLYVALENT BACTERIOPHAGE ... IN PATIENTS WITH ARS</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CYstic Fibrosis bacterioPHage study at Yale (CYPHY)</t>
+          <t>CLINICAL AND LABORATORY JUSTIFICATION FOR USE OF POLYVALENT BACTERIOPHAGE IN TECHNIQUE OF DELAYED PRESCRIBING OF ANTIBIOTICS IN PATIENTS WITH ARS.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1504,32 +1504,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>EST-083</t>
+          <t>EST-207</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>PRO</t>
+          <t>ORG</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Protocolo de estudio: declara lo que se hara, sin resultados</t>
+          <t>Organismo distinto de P. aeruginosa, sin subgrupo separable</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>PHAGEFORCE Study Protocol. P. aeruginosa solo aparece en la introduccion.</t>
+          <t>PDF correcto ya instalado (Europace 2020;22(4):597, DOI 10.1093/europace/euz319). Es un EP CASE EXPRESS de UNA pagina: varon de 41 anos, Marfan, infeccion de bolsillo de DAI e injerto vascular. CERO menciones de Pseudomonas o aeruginosa, y no nombra NINGUN microorganismo. La version completa del caso no esta en la revista, sino en una pagina de e-learning de la ESC. Fila extraida por un solo revisor.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>viruses StudyProtocol ... (The PHAGEFORCE Study Protocol)</t>
+          <t>A vacuum assisted closure treatment was initiated combined with antibiotics. Since no infection control was achieved, local application of a bacteriophage therapy was added.</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bacteriophage Therapy for Difficult-to-Treat Infections: The Implementation of a Multidisciplinary Phage Task Force (The PHAGEFORCE Study Protocol).</t>
+          <t>Successful bacteriophage treatment of infection involving cardiac implantable electronic device and aortic graft: a Trojan horse concept.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1546,32 +1546,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>EST-122</t>
+          <t>EST-212</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PRO</t>
+          <t>ORG</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Protocolo de estudio: declara lo que se hara, sin resultados</t>
+          <t>Organismo distinto de P. aeruginosa, sin subgrupo separable</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>STAMP study protocol, abierto de un solo brazo. 80 ocurrencias de "will be".</t>
+          <t>Espectro de SniPha 360; los cultivos dieron otra cosa.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>protocol for an open-label, single-arm ...</t>
+          <t>microbiological analysis of intraoperative samples confirmed infection with Staphylococcus aureus and Proteus mirabilis</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Standardised treatment and monitoring protocol to assess safety and tolerability of bacteriophage therapy for adult and paediatric patients (STAMP stu</t>
+          <t>Local Treatment of Driveline Infection with Bacteriophages</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1588,47 +1588,215 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>EST-035</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Protocolo de estudio: declara lo que se hara, sin resultados</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>STUDY PROTOCOL en Trials (2022). 99 ocurrencias de "will be".</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Safety and microbiological activity of phage therapy in persons with cystic fibrosis</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Safety and microbiological activity of phage therapy in persons with cystic fibrosis colonized with Pseudomonas aeruginosa: study protocol for a phase</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EST-052</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Protocolo de estudio: declara lo que se hara, sin resultados</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Documento de protocolo CYPHY, Yale, version 11. 223 ocurrencias de "will be".</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Protocol Number: 2000029160 November 29, 2022 Version 11</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>CYstic Fibrosis bacterioPHage study at Yale (CYPHY)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EST-083</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Protocolo de estudio: declara lo que se hara, sin resultados</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>PHAGEFORCE Study Protocol. P. aeruginosa solo aparece en la introduccion.</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>viruses StudyProtocol ... (The PHAGEFORCE Study Protocol)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Bacteriophage Therapy for Difficult-to-Treat Infections: The Implementation of a Multidisciplinary Phage Task Force (The PHAGEFORCE Study Protocol).</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>EST-122</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Protocolo de estudio: declara lo que se hara, sin resultados</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>STAMP study protocol, abierto de un solo brazo. 80 ocurrencias de "will be".</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>protocol for an open-label, single-arm ...</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Standardised treatment and monitoring protocol to assess safety and tolerability of bacteriophage therapy for adult and paediatric patients (STAMP stu</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>EST-060</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>REV</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Revision narrativa o comentario, sin datos primarios propios</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>Pieza de opinion con revision de la literatura y experiencia propia.</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>viruses Opinion ... Personal Experience and Literature Review</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>Clinical Indications and Compassionate Use of Phage Therapy: Personal Experience and Literature Review with a Focus on Osteoarticular Infections.</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>D. Valdiviezo y N. Trelles</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H23"/>
+  <autoFilter ref="A1:H27"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/verificables revisión sistemática/S16_excluidos_tras_leer_el_texto_completo.xlsx
+++ b/verificables revisión sistemática/S16_excluidos_tras_leer_el_texto_completo.xlsx
@@ -649,7 +649,7 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-01</t>
+          <t>Generado el 2026-09-02</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S16_excluidos_tras_leer_el_texto_completo.xlsx
+++ b/verificables revisión sistemática/S16_excluidos_tras_leer_el_texto_completo.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$H$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$H$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -529,7 +529,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>26 filas de datos</t>
+          <t>27 filas de datos</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1462,7 +1462,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>EST-178</t>
+          <t>EST-177</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1477,17 +1477,17 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Cero menciones en 22.705 caracteres, en ninguna grafia. Rinosinusitis aguda.</t>
+          <t>Texto completo leido en linea el 1 de septiembre de 2026, en la version INGLESA del propio editor (otolaryngologypl.com/article/150084/en), no una traduccion. Son 40 pacientes adultos con rinosinusitis cronica con polipos nasales, operados por cirugia endoscopica funcional; 20 recibieron gel intranasal con fagos y 20 placebo. P. aeruginosa aparece UNA sola vez en todo el articulo, en el espectro declarado del producto: el gel Otophag contiene 32 tipos de fagos y la lista de bacterias que inhibe la incluye. Lo que se midio en los pacientes fue Streptococci, Enterobacteriaceae y Staphylococci. Ningun paciente tiene P. aeruginosa documentada. Mismo patron que las otras diez exclusiones ORG. El idioma SI cumple: el editor publica version inglesa propia.</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>USE OF POLYVALENT BACTERIOPHAGE ... IN PATIENTS WITH ARS</t>
+          <t>The "Otophag" (Micromir, Russia) intranasal gel with bacteriophages contains a complex of 32 types of bacteriophages that inhibit the growth of a large number of pathogenic bacteria (... Pseudomonas aeruginosa spp., Staphylococcus aureus spp., Streptococcus pyogenes spp.)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>CLINICAL AND LABORATORY JUSTIFICATION FOR USE OF POLYVALENT BACTERIOPHAGE IN TECHNIQUE OF DELAYED PRESCRIBING OF ANTIBIOTICS IN PATIENTS WITH ARS.</t>
+          <t>A randomized, double-blind, placebo- -controlled study to investigate the use of bacteriophages in patients with chronic rhinosinusitis with nasal pol</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1497,14 +1497,14 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>EST-207</t>
+          <t>EST-178</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1519,17 +1519,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>PDF correcto ya instalado (Europace 2020;22(4):597, DOI 10.1093/europace/euz319). Es un EP CASE EXPRESS de UNA pagina: varon de 41 anos, Marfan, infeccion de bolsillo de DAI e injerto vascular. CERO menciones de Pseudomonas o aeruginosa, y no nombra NINGUN microorganismo. La version completa del caso no esta en la revista, sino en una pagina de e-learning de la ESC. Fila extraida por un solo revisor.</t>
+          <t>Cero menciones en 22.705 caracteres, en ninguna grafia. Rinosinusitis aguda.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>A vacuum assisted closure treatment was initiated combined with antibiotics. Since no infection control was achieved, local application of a bacteriophage therapy was added.</t>
+          <t>USE OF POLYVALENT BACTERIOPHAGE ... IN PATIENTS WITH ARS</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Successful bacteriophage treatment of infection involving cardiac implantable electronic device and aortic graft: a Trojan horse concept.</t>
+          <t>CLINICAL AND LABORATORY JUSTIFICATION FOR USE OF POLYVALENT BACTERIOPHAGE IN TECHNIQUE OF DELAYED PRESCRIBING OF ANTIBIOTICS IN PATIENTS WITH ARS.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1546,7 +1546,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>EST-212</t>
+          <t>EST-207</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1561,17 +1561,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Espectro de SniPha 360; los cultivos dieron otra cosa.</t>
+          <t>PDF correcto ya instalado (Europace 2020;22(4):597, DOI 10.1093/europace/euz319). Es un EP CASE EXPRESS de UNA pagina: varon de 41 anos, Marfan, infeccion de bolsillo de DAI e injerto vascular. CERO menciones de Pseudomonas o aeruginosa, y no nombra NINGUN microorganismo. La version completa del caso no esta en la revista, sino en una pagina de e-learning de la ESC. Fila extraida por un solo revisor.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>microbiological analysis of intraoperative samples confirmed infection with Staphylococcus aureus and Proteus mirabilis</t>
+          <t>A vacuum assisted closure treatment was initiated combined with antibiotics. Since no infection control was achieved, local application of a bacteriophage therapy was added.</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Local Treatment of Driveline Infection with Bacteriophages</t>
+          <t>Successful bacteriophage treatment of infection involving cardiac implantable electronic device and aortic graft: a Trojan horse concept.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1588,32 +1588,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>EST-035</t>
+          <t>EST-212</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PRO</t>
+          <t>ORG</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Protocolo de estudio: declara lo que se hara, sin resultados</t>
+          <t>Organismo distinto de P. aeruginosa, sin subgrupo separable</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>STUDY PROTOCOL en Trials (2022). 99 ocurrencias de "will be".</t>
+          <t>Espectro de SniPha 360; los cultivos dieron otra cosa.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Safety and microbiological activity of phage therapy in persons with cystic fibrosis</t>
+          <t>microbiological analysis of intraoperative samples confirmed infection with Staphylococcus aureus and Proteus mirabilis</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Safety and microbiological activity of phage therapy in persons with cystic fibrosis colonized with Pseudomonas aeruginosa: study protocol for a phase</t>
+          <t>Local Treatment of Driveline Infection with Bacteriophages</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1630,7 +1630,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>EST-052</t>
+          <t>EST-035</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1645,17 +1645,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Documento de protocolo CYPHY, Yale, version 11. 223 ocurrencias de "will be".</t>
+          <t>STUDY PROTOCOL en Trials (2022). 99 ocurrencias de "will be".</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Protocol Number: 2000029160 November 29, 2022 Version 11</t>
+          <t>Safety and microbiological activity of phage therapy in persons with cystic fibrosis</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CYstic Fibrosis bacterioPHage study at Yale (CYPHY)</t>
+          <t>Safety and microbiological activity of phage therapy in persons with cystic fibrosis colonized with Pseudomonas aeruginosa: study protocol for a phase</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1672,7 +1672,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>EST-083</t>
+          <t>EST-052</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1687,17 +1687,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>PHAGEFORCE Study Protocol. P. aeruginosa solo aparece en la introduccion.</t>
+          <t>Documento de protocolo CYPHY, Yale, version 11. 223 ocurrencias de "will be".</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>viruses StudyProtocol ... (The PHAGEFORCE Study Protocol)</t>
+          <t>Protocol Number: 2000029160 November 29, 2022 Version 11</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bacteriophage Therapy for Difficult-to-Treat Infections: The Implementation of a Multidisciplinary Phage Task Force (The PHAGEFORCE Study Protocol).</t>
+          <t>CYstic Fibrosis bacterioPHage study at Yale (CYPHY)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1714,7 +1714,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>EST-122</t>
+          <t>EST-083</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1729,17 +1729,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>STAMP study protocol, abierto de un solo brazo. 80 ocurrencias de "will be".</t>
+          <t>PHAGEFORCE Study Protocol. P. aeruginosa solo aparece en la introduccion.</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>protocol for an open-label, single-arm ...</t>
+          <t>viruses StudyProtocol ... (The PHAGEFORCE Study Protocol)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Standardised treatment and monitoring protocol to assess safety and tolerability of bacteriophage therapy for adult and paediatric patients (STAMP stu</t>
+          <t>Bacteriophage Therapy for Difficult-to-Treat Infections: The Implementation of a Multidisciplinary Phage Task Force (The PHAGEFORCE Study Protocol).</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1756,47 +1756,89 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>EST-122</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Protocolo de estudio: declara lo que se hara, sin resultados</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>STAMP study protocol, abierto de un solo brazo. 80 ocurrencias de "will be".</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>protocol for an open-label, single-arm ...</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Standardised treatment and monitoring protocol to assess safety and tolerability of bacteriophage therapy for adult and paediatric patients (STAMP stu</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>EST-060</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>REV</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Revision narrativa o comentario, sin datos primarios propios</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>Pieza de opinion con revision de la literatura y experiencia propia.</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>viruses Opinion ... Personal Experience and Literature Review</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>Clinical Indications and Compassionate Use of Phage Therapy: Personal Experience and Literature Review with a Focus on Osteoarticular Infections.</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>D. Valdiviezo y N. Trelles</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H27"/>
+  <autoFilter ref="A1:H28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/verificables revisión sistemática/S16_excluidos_tras_leer_el_texto_completo.xlsx
+++ b/verificables revisión sistemática/S16_excluidos_tras_leer_el_texto_completo.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$H$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$H$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -529,7 +529,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>27 filas de datos</t>
+          <t>29 filas de datos</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1100,49 +1100,49 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>EST-037</t>
+          <t>EST-118</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>OFF</t>
+          <t>NOREC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No evalua fagoterapia en pacientes (encuesta, epidemiologia, prensa, otra terapia)</t>
+          <t>Texto completo no recuperado: no se pudo verificar contra el articulo</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Caso de shock septico por P. aeruginosa PDR donde el fago solo se menciona como opcion no disponible.</t>
+          <t>No se consiguio el texto completo. NO falla ningun criterio de §2.2: se excluye por no haberse podido leer. Comprobada su disponibilidad contra Europe PMC, OpenAlex y Semantic Scholar; la unica copia esta en el Zurich Open Repository, es la version ENVIADA --previa a revision por pares-- y el repositorio esta tras una barrera anti-bots. Decision de D. Valdiviezo del 2026-09-02, tomada conociendo que el criterio aplicado de forma consistente sacaria a los 26 no recuperados.</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Experimental therapies, including bacteriophages ... remain unavailable in most clinical settings</t>
+          <t>(no hay articulo que citar: ese es el motivo)</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pan-Resistant Pseudomonas aeruginosa Septic Shock in a Critically Ill Patient: A Case Report.</t>
+          <t>Intravesical bacteriophages for treating urinary tract infections in patients undergoing transurethral resection of the prostate: a randomised, placeb</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>D. Valdiviezo y N. Trelles</t>
+          <t>D. Valdiviezo</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>EST-185</t>
+          <t>EST-037</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1157,17 +1157,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Articulo de cirugia reconstructiva de mediastinitis esternal. UNA mencion de fago en 43.000 caracteres, en una celda de tabla entre ocho antimicrobianos.</t>
+          <t>Caso de shock septico por P. aeruginosa PDR donde el fago solo se menciona como opcion no disponible.</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Avibactam, bacteriophage therapy, ceftazidime, colistin, meropenem, minocycline, piperacillin-tazobactam</t>
+          <t>Experimental therapies, including bacteriophages ... remain unavailable in most clinical settings</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>The management of sternal mediastinitis in heart and lung transplant patients: An 8-year experience and application of reconstructive algorithm</t>
+          <t>Pan-Resistant Pseudomonas aeruginosa Septic Shock in a Critically Ill Patient: A Case Report.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1184,32 +1184,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EST-076</t>
+          <t>EST-185</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ORG</t>
+          <t>OFF</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Organismo distinto de P. aeruginosa, sin subgrupo separable</t>
+          <t>No evalua fagoterapia en pacientes (encuesta, epidemiologia, prensa, otra terapia)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Cero menciones. Artroplastias infectadas por Staphylococcus.</t>
+          <t>Articulo de cirugia reconstructiva de mediastinitis esternal. UNA mencion de fago en 43.000 caracteres, en una celda de tabla entre ocho antimicrobianos.</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Keywords: periprosthetic joint infections; Staphylococcus</t>
+          <t>Avibactam, bacteriophage therapy, ceftazidime, colistin, meropenem, minocycline, piperacillin-tazobactam</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Experience Using Adjuvant Bacteriophage Therapy for the Treatment of 10 Recalcitrant Periprosthetic Joint Infections: A Case Series.</t>
+          <t>The management of sternal mediastinitis in heart and lung transplant patients: An 8-year experience and application of reconstructive algorithm</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1226,7 +1226,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EST-086</t>
+          <t>EST-076</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1241,13 +1241,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Cepa de referencia ATCC 27853 usada para fabricar el coctel; pacientes de COVID-19.</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
+          <t>Cero menciones. Artroplastias infectadas por Staphylococcus.</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Keywords: periprosthetic joint infections; Staphylococcus</t>
+        </is>
+      </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Inhalation phage therapy as a new approach to preventing secondary bacterial pneumonia in patients with moderate to severe COVID-19: A double-blind cl</t>
+          <t>Experience Using Adjuvant Bacteriophage Therapy for the Treatment of 10 Recalcitrant Periprosthetic Joint Infections: A Case Series.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1264,7 +1268,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>EST-101</t>
+          <t>EST-086</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1279,17 +1283,13 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Ninos ventilados; los criterios excluian neumonia bacteriana; cultivos negativos.</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>excluded children with bacterial pneumonia</t>
-        </is>
-      </c>
+          <t>Cepa de referencia ATCC 27853 usada para fabricar el coctel; pacientes de COVID-19.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>The Efficacy of Inhaled Phage Cocktail to Prevent Ventilator-Associated Pneumonia in Children: A Double-Blind Clinical Trial</t>
+          <t>Inhalation phage therapy as a new approach to preventing secondary bacterial pneumonia in patients with moderate to severe COVID-19: A double-blind cl</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1306,7 +1306,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>EST-126</t>
+          <t>EST-101</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1321,17 +1321,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Etiqueta del piobacteriofago y una referencia. 212 ninos con amigdalitis aguda.</t>
+          <t>Ninos ventilados; los criterios excluian neumonia bacteriana; cultivos negativos.</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>the drug is recommended for use in treating ...</t>
+          <t>excluded children with bacterial pneumonia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Application of bacteriophage therapy in the treatment of children with acute tonsillitis</t>
+          <t>The Efficacy of Inhaled Phage Cocktail to Prevent Ventilator-Associated Pneumonia in Children: A Double-Blind Clinical Trial</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1348,7 +1348,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>EST-130</t>
+          <t>EST-126</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1363,13 +1363,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Solo en la lista de referencias.</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
+          <t>Etiqueta del piobacteriofago y una referencia. 212 ninos con amigdalitis aguda.</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>the drug is recommended for use in treating ...</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Prolonged disease remission of the chronic immunological skin disorder hidradenitis suppurativa with adjunctive bacteriophage therapy.</t>
+          <t>Application of bacteriophage therapy in the treatment of children with acute tonsillitis</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1386,7 +1390,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>EST-131</t>
+          <t>EST-130</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1401,13 +1405,13 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Solo en la lista de referencias, sus tres menciones.</t>
+          <t>Solo en la lista de referencias.</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Results of TOR001: An open-label single patient study using targeted bacteriophage therapy for the treatment of a chronic urinary tract infection</t>
+          <t>Prolonged disease remission of the chronic immunological skin disorder hidradenitis suppurativa with adjunctive bacteriophage therapy.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1424,7 +1428,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>EST-159</t>
+          <t>EST-131</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1439,13 +1443,13 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Espectro del coctel SniPha 360.</t>
+          <t>Solo en la lista de referencias, sus tres menciones.</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bacteriophage-Enriched Galenic for Intrapericardial Ventricular Assist Device Infection</t>
+          <t>Results of TOR001: An open-label single patient study using targeted bacteriophage therapy for the treatment of a chronic urinary tract infection</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1462,7 +1466,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>EST-177</t>
+          <t>EST-159</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1477,17 +1481,13 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Texto completo leido en linea el 1 de septiembre de 2026, en la version INGLESA del propio editor (otolaryngologypl.com/article/150084/en), no una traduccion. Son 40 pacientes adultos con rinosinusitis cronica con polipos nasales, operados por cirugia endoscopica funcional; 20 recibieron gel intranasal con fagos y 20 placebo. P. aeruginosa aparece UNA sola vez en todo el articulo, en el espectro declarado del producto: el gel Otophag contiene 32 tipos de fagos y la lista de bacterias que inhibe la incluye. Lo que se midio en los pacientes fue Streptococci, Enterobacteriaceae y Staphylococci. Ningun paciente tiene P. aeruginosa documentada. Mismo patron que las otras diez exclusiones ORG. El idioma SI cumple: el editor publica version inglesa propia.</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>The "Otophag" (Micromir, Russia) intranasal gel with bacteriophages contains a complex of 32 types of bacteriophages that inhibit the growth of a large number of pathogenic bacteria (... Pseudomonas aeruginosa spp., Staphylococcus aureus spp., Streptococcus pyogenes spp.)</t>
-        </is>
-      </c>
+          <t>Espectro del coctel SniPha 360.</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>A randomized, double-blind, placebo- -controlled study to investigate the use of bacteriophages in patients with chronic rhinosinusitis with nasal pol</t>
+          <t>Bacteriophage-Enriched Galenic for Intrapericardial Ventricular Assist Device Infection</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1497,14 +1497,14 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>EST-178</t>
+          <t>EST-177</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1519,17 +1519,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Cero menciones en 22.705 caracteres, en ninguna grafia. Rinosinusitis aguda.</t>
+          <t>Texto completo leido en linea el 1 de septiembre de 2026, en la version INGLESA del propio editor (otolaryngologypl.com/article/150084/en), no una traduccion. Son 40 pacientes adultos con rinosinusitis cronica con polipos nasales, operados por cirugia endoscopica funcional; 20 recibieron gel intranasal con fagos y 20 placebo. P. aeruginosa aparece UNA sola vez en todo el articulo, en el espectro declarado del producto: el gel Otophag contiene 32 tipos de fagos y la lista de bacterias que inhibe la incluye. Lo que se midio en los pacientes fue Streptococci, Enterobacteriaceae y Staphylococci. Ningun paciente tiene P. aeruginosa documentada. Mismo patron que las otras diez exclusiones ORG. El idioma SI cumple: el editor publica version inglesa propia.</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>USE OF POLYVALENT BACTERIOPHAGE ... IN PATIENTS WITH ARS</t>
+          <t>The "Otophag" (Micromir, Russia) intranasal gel with bacteriophages contains a complex of 32 types of bacteriophages that inhibit the growth of a large number of pathogenic bacteria (... Pseudomonas aeruginosa spp., Staphylococcus aureus spp., Streptococcus pyogenes spp.)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>CLINICAL AND LABORATORY JUSTIFICATION FOR USE OF POLYVALENT BACTERIOPHAGE IN TECHNIQUE OF DELAYED PRESCRIBING OF ANTIBIOTICS IN PATIENTS WITH ARS.</t>
+          <t>A randomized, double-blind, placebo- -controlled study to investigate the use of bacteriophages in patients with chronic rhinosinusitis with nasal pol</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1539,14 +1539,14 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>EST-207</t>
+          <t>EST-178</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1561,17 +1561,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>PDF correcto ya instalado (Europace 2020;22(4):597, DOI 10.1093/europace/euz319). Es un EP CASE EXPRESS de UNA pagina: varon de 41 anos, Marfan, infeccion de bolsillo de DAI e injerto vascular. CERO menciones de Pseudomonas o aeruginosa, y no nombra NINGUN microorganismo. La version completa del caso no esta en la revista, sino en una pagina de e-learning de la ESC. Fila extraida por un solo revisor.</t>
+          <t>Cero menciones en 22.705 caracteres, en ninguna grafia. Rinosinusitis aguda.</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>A vacuum assisted closure treatment was initiated combined with antibiotics. Since no infection control was achieved, local application of a bacteriophage therapy was added.</t>
+          <t>USE OF POLYVALENT BACTERIOPHAGE ... IN PATIENTS WITH ARS</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Successful bacteriophage treatment of infection involving cardiac implantable electronic device and aortic graft: a Trojan horse concept.</t>
+          <t>CLINICAL AND LABORATORY JUSTIFICATION FOR USE OF POLYVALENT BACTERIOPHAGE IN TECHNIQUE OF DELAYED PRESCRIBING OF ANTIBIOTICS IN PATIENTS WITH ARS.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1588,7 +1588,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>EST-212</t>
+          <t>EST-207</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1603,17 +1603,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Espectro de SniPha 360; los cultivos dieron otra cosa.</t>
+          <t>PDF correcto ya instalado (Europace 2020;22(4):597, DOI 10.1093/europace/euz319). Es un EP CASE EXPRESS de UNA pagina: varon de 41 anos, Marfan, infeccion de bolsillo de DAI e injerto vascular. CERO menciones de Pseudomonas o aeruginosa, y no nombra NINGUN microorganismo. La version completa del caso no esta en la revista, sino en una pagina de e-learning de la ESC. Fila extraida por un solo revisor.</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>microbiological analysis of intraoperative samples confirmed infection with Staphylococcus aureus and Proteus mirabilis</t>
+          <t>A vacuum assisted closure treatment was initiated combined with antibiotics. Since no infection control was achieved, local application of a bacteriophage therapy was added.</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Local Treatment of Driveline Infection with Bacteriophages</t>
+          <t>Successful bacteriophage treatment of infection involving cardiac implantable electronic device and aortic graft: a Trojan horse concept.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1630,32 +1630,32 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>EST-035</t>
+          <t>EST-212</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>PRO</t>
+          <t>ORG</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Protocolo de estudio: declara lo que se hara, sin resultados</t>
+          <t>Organismo distinto de P. aeruginosa, sin subgrupo separable</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>STUDY PROTOCOL en Trials (2022). 99 ocurrencias de "will be".</t>
+          <t>Espectro de SniPha 360; los cultivos dieron otra cosa.</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Safety and microbiological activity of phage therapy in persons with cystic fibrosis</t>
+          <t>microbiological analysis of intraoperative samples confirmed infection with Staphylococcus aureus and Proteus mirabilis</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Safety and microbiological activity of phage therapy in persons with cystic fibrosis colonized with Pseudomonas aeruginosa: study protocol for a phase</t>
+          <t>Local Treatment of Driveline Infection with Bacteriophages</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1672,7 +1672,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>EST-052</t>
+          <t>EST-035</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1687,17 +1687,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Documento de protocolo CYPHY, Yale, version 11. 223 ocurrencias de "will be".</t>
+          <t>STUDY PROTOCOL en Trials (2022). 99 ocurrencias de "will be".</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Protocol Number: 2000029160 November 29, 2022 Version 11</t>
+          <t>Safety and microbiological activity of phage therapy in persons with cystic fibrosis</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>CYstic Fibrosis bacterioPHage study at Yale (CYPHY)</t>
+          <t>Safety and microbiological activity of phage therapy in persons with cystic fibrosis colonized with Pseudomonas aeruginosa: study protocol for a phase</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1714,7 +1714,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>EST-083</t>
+          <t>EST-052</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1729,17 +1729,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>PHAGEFORCE Study Protocol. P. aeruginosa solo aparece en la introduccion.</t>
+          <t>Documento de protocolo CYPHY, Yale, version 11. 223 ocurrencias de "will be".</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>viruses StudyProtocol ... (The PHAGEFORCE Study Protocol)</t>
+          <t>Protocol Number: 2000029160 November 29, 2022 Version 11</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bacteriophage Therapy for Difficult-to-Treat Infections: The Implementation of a Multidisciplinary Phage Task Force (The PHAGEFORCE Study Protocol).</t>
+          <t>CYstic Fibrosis bacterioPHage study at Yale (CYPHY)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1756,7 +1756,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>EST-122</t>
+          <t>EST-083</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1771,17 +1771,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>STAMP study protocol, abierto de un solo brazo. 80 ocurrencias de "will be".</t>
+          <t>PHAGEFORCE Study Protocol. P. aeruginosa solo aparece en la introduccion.</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>protocol for an open-label, single-arm ...</t>
+          <t>viruses StudyProtocol ... (The PHAGEFORCE Study Protocol)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Standardised treatment and monitoring protocol to assess safety and tolerability of bacteriophage therapy for adult and paediatric patients (STAMP stu</t>
+          <t>Bacteriophage Therapy for Difficult-to-Treat Infections: The Implementation of a Multidisciplinary Phage Task Force (The PHAGEFORCE Study Protocol).</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1798,47 +1798,131 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>EST-122</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Protocolo de estudio: declara lo que se hara, sin resultados</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>STAMP study protocol, abierto de un solo brazo. 80 ocurrencias de "will be".</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>protocol for an open-label, single-arm ...</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Standardised treatment and monitoring protocol to assess safety and tolerability of bacteriophage therapy for adult and paediatric patients (STAMP stu</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>EST-060</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>REV</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Revision narrativa o comentario, sin datos primarios propios</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D29" t="inlineStr">
         <is>
           <t>Pieza de opinion con revision de la literatura y experiencia propia.</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>viruses Opinion ... Personal Experience and Literature Review</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>Clinical Indications and Compassionate Use of Phage Therapy: Personal Experience and Literature Review with a Focus on Osteoarticular Infections.</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>D. Valdiviezo y N. Trelles</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>EST-205</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>REV</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Revision narrativa o comentario, sin datos primarios propios</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Editorial de dos paginas (137-138) firmado por un solo autor. SciELO lo indexa literalmente como «Tipo de literatura: Editorial» y «No citable». Un editorial no aporta datos primarios propios, que es lo que §2.2 exige. El texto no se pudo leer --scielo.sld.cu no resuelve ni desde el canal ni desde el navegador-- asi que la exclusion se apoya en la indexacion del propio repositorio, no en el articulo.</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>SciELO: «Tipo de literatura: Editorial»; «Citables y no citables: No citable»; paginas 137-138</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Beneficios obtenidos con el empleo de bacteriófagos en el tratamiento de infecciones crónicas</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H28"/>
+  <autoFilter ref="A1:H30"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/verificables revisión sistemática/S16_excluidos_tras_leer_el_texto_completo.xlsx
+++ b/verificables revisión sistemática/S16_excluidos_tras_leer_el_texto_completo.xlsx
@@ -649,7 +649,7 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-02</t>
+          <t>Generado el 2026-09-14</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S16_excluidos_tras_leer_el_texto_completo.xlsx
+++ b/verificables revisión sistemática/S16_excluidos_tras_leer_el_texto_completo.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$H$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$H$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -529,7 +529,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>29 filas de datos</t>
+          <t>39 filas de datos</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1921,8 +1921,428 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>EST-072</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ORG</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Organismo distinto de P. aeruginosa, sin subgrupo separable</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Organismo distinto de P. aeruginosa, sin subgrupo separable. Verificado sobre la ficha completa del registro (ClinicalTrials.gov NCT06605651), bajada el 2026-09-14 y guardada en revision_sistematica/textos_completos/registros/. El estudio entro al corpus como ficha de registro sin resumen ni MeSH, de modo que el cribado no tuvo con que descartarlo.</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>[eligibilityCriteria] Inclusion Criteria: 1. Male or female ≥ 18 years 2. Knee or Hip PJI according to EBJIS (European Bone and Joint Infection) or ICM (International Consensus Meeting) guidelines 3. Monobacterial Infection due to S. aureus 4. Without preoperative diagnosis of superinfection due to another pathogen if treatment is administered at the end of the DAIR (presence of a contaminant is not considered clinically relevant) 5. Wi...</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Proof of Concept Study to Assess Safety and Efficacy of Phage Therapy in Hip or Knee Prosthetic Joint Infections Due to Staphylococcus Aureus Treated by DAIR.</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>DANNY JAVIER VALDIVIEZO VERDUGO y NATALY ELIZABETH TRELLES AVILA</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>EST-138</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>ORG</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Organismo distinto de P. aeruginosa, sin subgrupo separable</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Organismo distinto de P. aeruginosa, sin subgrupo separable. Verificado sobre la ficha completa del registro (CTIS 2022-500541-24-00), bajada el 2026-09-14 y guardada en revision_sistematica/textos_completos/registros/. El estudio entro al corpus como ficha de registro sin resumen ni MeSH, de modo que el cribado no tuvo con que descartarlo.</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>[publicTitle] Comparison of the efficacy of standard treatment associated with phage therapy versus standard treatment plus placebo for diabetic foot ulcers infected by Staphylococcus aureus</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>PHRC-N/2015/AS-01 - Comparison of the efficacy of standard treatment associated with phage therapy versus standard treatment plus placebo for diabetic foot ulcers infected by Staph</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>DANNY JAVIER VALDIVIEZO VERDUGO y NATALY ELIZABETH TRELLES AVILA</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>EST-150</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ORG</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Organismo distinto de P. aeruginosa, sin subgrupo separable</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Organismo distinto de P. aeruginosa, sin subgrupo separable. Verificado sobre la ficha completa del registro (ClinicalTrials.gov NCT06827041), bajada el 2026-09-14 y guardada en revision_sistematica/textos_completos/registros/. El estudio entro al corpus como ficha de registro sin resumen ni MeSH, de modo que el cribado no tuvo con que descartarlo.</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>[officialTitle] Use of Phage Therapy for Treatment of a Life-Threatening, Multidrug Resistant Staphylococcus Epidermidis Chronic Periprosthetic Joint Infection: an N-of-1 Trial</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Use of Phage Therapy for Treatment of a Periprosthetic Joint Infection</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>DANNY JAVIER VALDIVIEZO VERDUGO y NATALY ELIZABETH TRELLES AVILA</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>EST-182</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>ORG</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Organismo distinto de P. aeruginosa, sin subgrupo separable</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Organismo distinto de P. aeruginosa, sin subgrupo separable. Verificado sobre la ficha completa del registro (ClinicalTrials.gov NCT06938867), bajada el 2026-09-14 y guardada en revision_sistematica/textos_completos/registros/. El estudio entro al corpus como ficha de registro sin resumen ni MeSH, de modo que el cribado no tuvo con que descartarlo.</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>[officialTitle] ...fficacy of Oral Administration of SNIPR001 in Patients With Hematologic Malignancy Scheduled for Allogeneic Hematopoietic Stem-Cell Transplantation Receiving Fluoroquinolone Prophylaxis and Harboring Fluoroquinolone-Resistant Escherichia Coli Pre-Transplant</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Phase 1b/2a Randomized Double-blind Study to Investigate Safety Tolerability PK PD Preliminary Efficacy of Oral Administration of SNIPR001 in Patients With Hematologic Malignancy Scheduled for Allogeneic Hematopoietic Stem-Cell Transplant Receiving FQ Prophylaxis &amp; Harboring FQR Ecoli Pre-Transplant</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>DANNY JAVIER VALDIVIEZO VERDUGO y NATALY ELIZABETH TRELLES AVILA</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>EST-204</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>ORG</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Organismo distinto de P. aeruginosa, sin subgrupo separable</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Organismo distinto de P. aeruginosa, sin subgrupo separable. Verificado sobre la ficha completa del registro (ClinicalTrials.gov NCT00937274), bajada el 2026-09-14 y guardada en revision_sistematica/textos_completos/registros/. El estudio entro al corpus como ficha de registro sin resumen ni MeSH, de modo que el cribado no tuvo con que descartarlo.</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>[officialTitle] Randomized, Double Blind Placebo-controlled Studies to Evaluate the Effect of an Orally-fed Escherichia Coli (E. Coli) Phage in the Management of ETEC and EPEC Induced Diarrhea in Children</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Antibacterial Treatment Against Diarrhea in Oral Rehydration Solution</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>DANNY JAVIER VALDIVIEZO VERDUGO y NATALY ELIZABETH TRELLES AVILA</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>EST-210</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>ORG</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Organismo distinto de P. aeruginosa, sin subgrupo separable</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Organismo distinto de P. aeruginosa, sin subgrupo separable. Verificado sobre la ficha completa del registro (ClinicalTrials.gov NCT05277350), bajada el 2026-09-14 y guardada en revision_sistematica/textos_completos/registros/. El estudio entro al corpus como ficha de registro sin resumen ni MeSH, de modo que el cribado no tuvo con que descartarlo.</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>[eligibilityCriteria] ...ant organ abnormality, or disease diagnosis, as per Investigator discretion * No clinically significant abnormalities indicated by safety laboratory test results * Age between 18 years and 65 years * E. coli present in feces sample * Normal defecation pattern (at least once daily) * Willing to participate in the study and provide fecal samples Exclusion Criteria: * Treatment with antibiotics or any other prescription medicati...</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>A Study Investigating the Safety, Recovery, and Pharmacodynamics of Multiple Oral Administrations of SNIPR001 in Healthy Subjects</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>DANNY JAVIER VALDIVIEZO VERDUGO y NATALY ELIZABETH TRELLES AVILA</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>EST-211</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>No evalua fagoterapia en pacientes (encuesta, epidemiologia, prensa, otra terapia)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>No evalua fagoterapia en pacientes (encuesta, epidemiologia, prensa, otra terapia). Verificado sobre la ficha completa del registro (ClinicalTrials.gov NCT05618418), bajada el 2026-09-14 y guardada en revision_sistematica/textos_completos/registros/. El estudio entro al corpus como ficha de registro sin resumen ni MeSH, de modo que el cribado no tuvo con que descartarlo.</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>[briefSummary] ...ate with few treatment options improving survival. Recently certain bacterial strains has been correlated to survival in patients with alcoholic hepatitis. In the BATTLE-trial the investigators will investigate if certain bacteria are correlated to decreased chance of survival in patients with alcoholic hepatitis.</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>BActeriophages To Treat Liver Disease Eliminating Harmful Bacteria (BATTLE)</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>DANNY JAVIER VALDIVIEZO VERDUGO y NATALY ELIZABETH TRELLES AVILA</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>EST-213</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>OFF</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>No evalua fagoterapia en pacientes (encuesta, epidemiologia, prensa, otra terapia)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>No evalua fagoterapia en pacientes (encuesta, epidemiologia, prensa, otra terapia). Verificado sobre la ficha completa del registro (ClinicalTrials.gov NCT05314426), bajada el 2026-09-14 y guardada en revision_sistematica/textos_completos/registros/. El estudio entro al corpus como ficha de registro sin resumen ni MeSH, de modo que el cribado no tuvo con que descartarlo.</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>[briefSummary] The purpose of this study is to help scientists and clinicians discover answers to research questions related to antibiotic-resistant bacterial infections, and the role that phage therapy plays as a possible treatment.</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Mayo Clinic Phage Program Biobank</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>DANNY JAVIER VALDIVIEZO VERDUGO y NATALY ELIZABETH TRELLES AVILA</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>EST-216</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>ORG</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Organismo distinto de P. aeruginosa, sin subgrupo separable</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Organismo distinto de P. aeruginosa, sin subgrupo separable. Verificado sobre la ficha completa del registro (ClinicalTrials.gov NCT05967130), bajada el 2026-09-14 y guardada en revision_sistematica/textos_completos/registros/. El estudio entro al corpus como ficha de registro sin resumen ni MeSH, de modo que el cribado no tuvo con que descartarlo.</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>[briefSummary] Urinary tract infections (UTIs) with extended-spectrum -lactamase (ESBL)-positive Enterobacteriums (ESBL-E) are a common infectious complication of renal transplant recipients, with 10% of patients suffering from UTIs with ESBL-E within the first year posttransplant. Moreover, recurrence rates of...</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Treatment Chronic UTI Post Kidney Transplant</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>DANNY JAVIER VALDIVIEZO VERDUGO y NATALY ELIZABETH TRELLES AVILA</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>EST-218</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>ORG</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Organismo distinto de P. aeruginosa, sin subgrupo separable</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Organismo distinto de P. aeruginosa, sin subgrupo separable. Verificado sobre la ficha completa del registro (ClinicalTrials.gov NCT07076238), bajada el 2026-09-14 y guardada en revision_sistematica/textos_completos/registros/. El estudio entro al corpus como ficha de registro sin resumen ni MeSH, de modo que el cribado no tuvo con que descartarlo.</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>[briefSummary] This study aims to identify biomarkers associated with response to phage therapy for refractory bacterial infections. This includes mycobacteriophage treatment for patients with nontuberculous mycobacterial infections. Blood and airway samples will be obtained from follow up visits of patients with refractory bacterial infections that are considered for phage therapy. Samples will be compared between those that re...</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Biomarkers of Phage Treatment Response in NTM and Other Infections</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>DANNY JAVIER VALDIVIEZO VERDUGO y NATALY ELIZABETH TRELLES AVILA</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H30"/>
+  <autoFilter ref="A1:H40"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/verificables revisión sistemática/S16_excluidos_tras_leer_el_texto_completo.xlsx
+++ b/verificables revisión sistemática/S16_excluidos_tras_leer_el_texto_completo.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$H$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$H$47</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -529,7 +529,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>39 filas de datos</t>
+          <t>46 filas de datos</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2341,8 +2341,302 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>EST-141</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>NOORG</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>La ficha de registro no declara ningun organismo: el criterio de P. aeruginosa no se puede verificar ni a favor ni en contra</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>La ficha de registro no declara ningun organismo: el criterio de P. aeruginosa no se puede verificar ni a favor ni en contra. Ficha completa de ClinicalTrials.gov NCT04682964, bajada el 2026-09-14 y guardada en revision_sistematica/textos_completos/registros/. El estudio entro al corpus como ficha de registro sin resumen ni MeSH, de modo que el cribado no tuvo con que descartarlo. La ficha SI nombra a P. aeruginosa, pero en el campo «briefSummary» y dentro del espectro litico declarado del preparado de fagos, no como la bacteria de los pacientes: los criterios de elegibilidad no exigen ningun organismo.</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>[briefSummary, donde se nombra] ...s. The drug causes the lysis of certain bacteria, including staphylococcus, enterococcus, streptococcus, enteropathogenic E. coli, Proteus vulgaris, Proteus mirabilis, Pseudomonas aeruginosa, Klebsiella pneumoniae and Klebsiella oxytoca. The choice of this drug was based on bacteriological studies. || [eligibilityCriteria, los criterios] Inclusion Criteria: * children from 3 to 14 years old. * children with sore throat. * children diagnosed with acute tonsillitis. * children diagnosed with acute respiratory infection (rhinitis, sinusitis, nasopharyngitis). * children with the opportunity to visit the outpatient clinic. * children with the ability to receive i...</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Bacteriophage Therapy in Tonsillitis</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>DANNY JAVIER VALDIVIEZO VERDUGO y NATALY ELIZABETH TRELLES AVILA</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>EST-148</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>NOORG</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>La ficha de registro no declara ningun organismo: el criterio de P. aeruginosa no se puede verificar ni a favor ni en contra</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>La ficha de registro no declara ningun organismo: el criterio de P. aeruginosa no se puede verificar ni a favor ni en contra. Ficha completa de ClinicalTrials.gov NCT05537519, bajada el 2026-09-14 y guardada en revision_sistematica/textos_completos/registros/. El estudio entro al corpus como ficha de registro sin resumen ni MeSH, de modo que el cribado no tuvo con que descartarlo. Comprobado sobre la ficha entera: «Pseudomonas» y «aeruginosa» no aparecen en NINGUN campo del registro.</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>[eligibilityCriteria] Inclusion Criteria: * Diagnosis of recurrent chronic urinary tract infections with severe long term effects * Can speak and understand English * Willing to follow the protocol Exclusion Criteria: * Stage 5 chronic kidney disease * Abnormal liver function tests * A urinary st...</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Phage Therapy for the Treatment of Urinary Tract Infection</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>DANNY JAVIER VALDIVIEZO VERDUGO y NATALY ELIZABETH TRELLES AVILA</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>EST-192</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>NOORG</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>La ficha de registro no declara ningun organismo: el criterio de P. aeruginosa no se puede verificar ni a favor ni en contra</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>La ficha de registro no declara ningun organismo: el criterio de P. aeruginosa no se puede verificar ni a favor ni en contra. Ficha completa de ClinicalTrials.gov NCT04325685, bajada el 2026-09-14 y guardada en revision_sistematica/textos_completos/registros/. El estudio entro al corpus como ficha de registro sin resumen ni MeSH, de modo que el cribado no tuvo con que descartarlo. Comprobado sobre la ficha entera: «Pseudomonas» y «aeruginosa» no aparecen en NINGUN campo del registro.</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>[eligibilityCriteria] Inclusion Criteria: \- invasive mechanical ventilation beyond 48 hours Exclusion Criteria: * hospital - acquired pneumonia * community - acquired pneumoniae * BMI \&gt; 35 kg/cm2 * pregnancy * tracheostomy * reintubation</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>The Effect of Supraglottic and Oropharyngeal Decontamination on the Incidence of Ventilator-associated Pneumonia</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>DANNY JAVIER VALDIVIEZO VERDUGO y NATALY ELIZABETH TRELLES AVILA</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>EST-203</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>NOORG</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>La ficha de registro no declara ningun organismo: el criterio de P. aeruginosa no se puede verificar ni a favor ni en contra</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>La ficha de registro no declara ningun organismo: el criterio de P. aeruginosa no se puede verificar ni a favor ni en contra. Ficha completa de ClinicalTrials.gov NCT00663091, bajada el 2026-09-14 y guardada en revision_sistematica/textos_completos/registros/. El estudio entro al corpus como ficha de registro sin resumen ni MeSH, de modo que el cribado no tuvo con que descartarlo. La ficha SI nombra a P. aeruginosa, pero en el campo «description» y dentro del espectro litico declarado del preparado de fagos, no como la bacteria de los pacientes: los criterios de elegibilidad no exigen ningun organismo.</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>[description, donde se nombra] WPP-201 is a pH neutral, polyvalent phage preparation, which contains 8 bacteriophages ("component bacteriophages" or "component phages") lytic for P. aeruginosa, S. aureus, and E. coli (Table 1). The cocktail contains a concentration of approximately 1 x 109 PFU/ml of each of the component monophages. The phage component of WPP-201 is rou... || [eligibilityCriteria, los criterios] Inclusion Criteria: 1. Subject must have evidence of hemosiderosis, stasis dermatitis, or dermato liposclerosis; AND edema in the lower extremity on which the wound is present. 2. Subject must be at least 18 years of age. 3. Subject must have a minimum life expectan...</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>A Prospective, Randomized, Double-Blind Controlled Study of WPP-201 for the Safety and Efficacy of Treatment of Venous Leg Ulcers</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>DANNY JAVIER VALDIVIEZO VERDUGO y NATALY ELIZABETH TRELLES AVILA</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>EST-209</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>NOORG</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>La ficha de registro no declara ningun organismo: el criterio de P. aeruginosa no se puede verificar ni a favor ni en contra</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>La ficha de registro no declara ningun organismo: el criterio de P. aeruginosa no se puede verificar ni a favor ni en contra. Ficha completa de ClinicalTrials.gov NCT04724603, bajada el 2026-09-14 y guardada en revision_sistematica/textos_completos/registros/. El estudio entro al corpus como ficha de registro sin resumen ni MeSH, de modo que el cribado no tuvo con que descartarlo. Comprobado sobre la ficha entera: «Pseudomonas» y «aeruginosa» no aparecen en NINGUN campo del registro.</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>[eligibilityCriteria] Inclusion Criteria: * patients having had a bone or joint or implant infection treated by phagotherapy and having had an adverse event Exclusion Criteria: \-</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Phage Safety Retrospective Cohort Study</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>DANNY JAVIER VALDIVIEZO VERDUGO y NATALY ELIZABETH TRELLES AVILA</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>EST-214</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>NOORG</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>La ficha de registro no declara ningun organismo: el criterio de P. aeruginosa no se puede verificar ni a favor ni en contra</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>La ficha de registro no declara ningun organismo: el criterio de P. aeruginosa no se puede verificar ni a favor ni en contra. Ficha completa de ClinicalTrials.gov NCT04650607, bajada el 2026-09-14 y guardada en revision_sistematica/textos_completos/registros/. El estudio entro al corpus como ficha de registro sin resumen ni MeSH, de modo que el cribado no tuvo con que descartarlo. Comprobado sobre la ficha entera: «Pseudomonas» y «aeruginosa» no aparecen en NINGUN campo del registro.</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>[eligibilityCriteria] Inclusion Criteria: * Patient 18 years of age or older with a serious infection treated at CRIOAc Lyon by phage therapy * Patient who did not object to participating in the study * Patients ayant un poids minimum de 46kg Exclusion Criteria: * Patients under guardianship/curatorship * Patients deprived of liberty * P...</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Phage Safety Cohort Study</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>DANNY JAVIER VALDIVIEZO VERDUGO y NATALY ELIZABETH TRELLES AVILA</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>EST-087</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>NOORG</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>La ficha de registro no declara ningun organismo: el criterio de P. aeruginosa no se puede verificar ni a favor ni en contra</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>La ficha de registro no declara ningun organismo: el criterio de P. aeruginosa no se puede verificar ni a favor ni en contra. Ficha completa de ClinicalTrials.gov NCT06185920, bajada el 2026-09-14 y guardada en revision_sistematica/textos_completos/registros/. El estudio entro al corpus como ficha de registro sin resumen ni MeSH, de modo que el cribado no tuvo con que descartarlo. Comprobado sobre la ficha entera: «Pseudomonas» y «aeruginosa» no aparecen en NINGUN campo del registro.</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>[eligibilityCriteria] Inclusion Criteria: * Patient with severe infection treated with bacteriophage in the Hospices Civils de Lyon from 01/01/2015 to 01/01/2033 * PHAGEinLYON Clinic cohort study information notice provided to the patient Exclusion Criteria: * Opposition of trial participant</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>PHAGEinLYON Clinic Cohort Study: a Descriptive Study of Severe Infections Treated With Phage Therapy at the HCL.</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>DANNY JAVIER VALDIVIEZO VERDUGO y NATALY ELIZABETH TRELLES AVILA</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H40"/>
+  <autoFilter ref="A1:H47"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/verificables revisión sistemática/S16_excluidos_tras_leer_el_texto_completo.xlsx
+++ b/verificables revisión sistemática/S16_excluidos_tras_leer_el_texto_completo.xlsx
@@ -649,7 +649,7 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-14</t>
+          <t>Generado el 2026-09-15</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S16_excluidos_tras_leer_el_texto_completo.xlsx
+++ b/verificables revisión sistemática/S16_excluidos_tras_leer_el_texto_completo.xlsx
@@ -649,7 +649,7 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-15</t>
+          <t>Generado el 2026-09-16</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S16_excluidos_tras_leer_el_texto_completo.xlsx
+++ b/verificables revisión sistemática/S16_excluidos_tras_leer_el_texto_completo.xlsx
@@ -649,7 +649,7 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-16</t>
+          <t>Generado el 2026-09-22</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S16_excluidos_tras_leer_el_texto_completo.xlsx
+++ b/verificables revisión sistemática/S16_excluidos_tras_leer_el_texto_completo.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$H$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$H$48</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -529,7 +529,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>46 filas de datos</t>
+          <t>47 filas de datos</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:H48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2635,8 +2635,50 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>EST-063</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>PRO</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Protocolo de estudio: declara lo que se hara, sin resultados</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Protocolo de ensayo sin resultados. Estructura de protocolo de BMJ Open (INTRODUCTION / METHODS AND ANALYSIS / Ethics and dissemination) y 71 apariciones de «will be», el mismo criterio con que se excluyeron EST-035, EST-052, EST-083 y EST-122. La nota firmada del dominio D5 ya lo decia: «Es un protocolo; aun no hay resultados.» Firmado por los dos revisores el 2026-09-22.</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>This study is designed to provide pilot data pertaining to safety and tolerability in children and thus allow for larger, dosing or placebo trial studies that will fulfil Australian legislation.</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Single-arm, open-labelled, safety and tolerability of intrabronchial and nebulised bacteriophage treatment in children with cystic fibrosis and Pseudomonas aeruginosa.</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H47"/>
+  <autoFilter ref="A1:H48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/verificables revisión sistemática/S16_excluidos_tras_leer_el_texto_completo.xlsx
+++ b/verificables revisión sistemática/S16_excluidos_tras_leer_el_texto_completo.xlsx
@@ -649,7 +649,7 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-22</t>
+          <t>Generado el 2026-09-23</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S16_excluidos_tras_leer_el_texto_completo.xlsx
+++ b/verificables revisión sistemática/S16_excluidos_tras_leer_el_texto_completo.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$H$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$H$52</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -529,7 +529,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>47 filas de datos</t>
+          <t>51 filas de datos</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-09-23</t>
+          <t>Generado el 2026-10-03</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:H52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2677,8 +2677,176 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>EST-009</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>ORG</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Organismo distinto de P. aeruginosa, sin subgrupo separable</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Ningún paciente con P. aeruginosa tratado con fagos. No contiene pseudomona. Lectura firmada del 2026-09-30: declarada no verificable / no aplica: en el paciente no se aisló P. aeruginosa (Staphylococcus, Enterococcus, Streptococcus); P. aeruginosa solo aparece en la composición de los productos Eliava. No hay antibiograma.</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Testing of prostatic secretion and semen samples revealed pathogenic bacteria in each case, which collectively included members of the Staphylococcal species such as Methicillin resistant Staphylococcus aureus (MRSA) and Staphylococcus haemolyticus, Enterococcus faecalis, and Streptococcus mitis, among others</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Case Report: Chronic Bacterial Prostatitis Treated With Phage Therapy After Multiple Failed Antibiotic Treatments.</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>EST-055</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>ORG</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Organismo distinto de P. aeruginosa, sin subgrupo separable</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Ningún paciente con P. aeruginosa tratado con fagos. No contiene pseudomona. Lectura firmada del 2026-09-30: no aplica / declarada no verificable: entre los patógenos aislados (Tabla 2: E. coli, K. pneumoniae, P. mirabilis, S. epidermidis, S. aureus) no hay P. aeruginosa; P. aeruginosa solo figura en la composición del producto Sextaphage. La resistencia «MDR» se describe de forma agregada para todo el estudio.</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Resistance rate (%). Antibiotics E. coli (n = 114) K. pneumoniae (n = 31) Proteus mirabilis (n = 20) S. epidermidis (n = 8) S. aureus (n = 5)</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Bacteriophage therapy in women with chronic recurrent cystitis caused by multidrug-resistant bacteria: A prospective, observational, comparative study</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>EST-181</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>ORG</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Organismo distinto de P. aeruginosa, sin subgrupo separable</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Ningún paciente con P. aeruginosa tratado con fagos. No contiene pseudomona. Lectura firmada del 2026-09-30: no aplica: el estudio solo incluye infecciones protésicas de cadera por Staphylococcus spp. (la etiología no estafilocócica es criterio de exclusión); no hay pacientes con P. aeruginosa ni clase de resistencia de esa especie.</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>PJI of non-staphylococcal etiology» (p. 4) | «Identified PJI bacteria were Staphylococcus spp</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Short-Term Outcomes of Phage-Antibiotic Combination Treatment in Adult Patients with Periprosthetic Hip Joint Infection.</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>EST-208</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>ORG</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Organismo distinto de P. aeruginosa, sin subgrupo separable</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Ningún paciente con P. aeruginosa tratado con fagos. No contiene pseudomona. Lectura firmada del 2026-09-30: no aplica: infección de LVAD por Staphylococcus aureus sensible a meticilina; P. aeruginosa solo aparece en la discusión como referencia a otros estudios, no en este paciente.</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Intraoperative culture samples tested positive for methicillin-susceptible Staphylococcus aureus.</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Treatment of chronic left ventricular assist device infection with local application of bacteriophages.</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H48"/>
+  <autoFilter ref="A1:H52"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/verificables revisión sistemática/S16_excluidos_tras_leer_el_texto_completo.xlsx
+++ b/verificables revisión sistemática/S16_excluidos_tras_leer_el_texto_completo.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$H$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$H$56</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -529,7 +529,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>51 filas de datos</t>
+          <t>55 filas de datos</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-03</t>
+          <t>Generado el 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2845,8 +2845,176 @@
         </is>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>EST-132</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>ORG</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Organismo distinto de P. aeruginosa, sin subgrupo separable</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Sin subgrupo separable de P. aeruginosa. La frase es la composición del cóctel empírico que se aplicó hasta tener el fago personalizado (p. 2). El artículo no dice cuántos pacientes tenían P. aeruginosa ni desglosa por organismo, y el criterio de población exige un subgrupo separable. Si sale: deja de ser uno de los 4 con grupo de comparación y sus juicios RoB 2 salen de la Tabla 7. no separa pacientes con Pseudomonas</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>a mixture of bacteriophages against isolates most commonly found in the ICU, such as Escherichia coli, Pseudomonas aeruginosa,</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Evaluation of the Potential Efficacy of Bacteriophage Therapy for the Management of Pressure Ulcers and Its Comparison to Conventional Therapy: A Randomized Controlled Trial</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>EST-045</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>NOREC</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Texto completo no recuperado: no se pudo verificar contra el articulo</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Idioma no verificable sobre el artículo: solo se probó el resumen en inglés, en una revista que no publica de forma nativa en inglés. Resumen en inglés (1 161 caracteres). DOI 10.20953/1729-9225-2017-4-49-54 → ficha inglesa del editor (phdynasty.ru/en/), que no enlaza el artículo ni declara su idioma. Sin texto completo: no es acceso abierto. SIN TEXTO COMPLETO</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>(no hay texto completo: el artículo no se ha podido leer)</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Concept of individualized medicine based on personalized phage therapy for intensive care unit patients suffering from healthcare-associated infections</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>EST-059</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>NOREC</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Texto completo no recuperado: no se pudo verificar contra el articulo</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Idioma no verificable sobre el artículo: solo se probó el resumen en inglés, en una revista que no publica de forma nativa en inglés. Resumen en inglés (1 337 caracteres). DOI 10.20953/1729-9225-2017-1-35-40 → ficha inglesa del editor, sin enlace al artículo. Zenodo 1997795 guarda un .docx de 17 756 bytes, que no se ha descargado. SIN TEXTO COMPLETO</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>(no hay texto completo: el artículo no se ha podido leer)</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Anti-phage antibody response in phage therapy against healthcare-associated infections (HAIs)</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>EST-173</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>NOREC</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Texto completo no recuperado: no se pudo verificar contra el articulo</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Idioma no verificable sobre el artículo: solo se probó el resumen en inglés, en una revista que no publica de forma nativa en inglés. Resumen en inglés (1 994 caracteres). Sin DOI ni otro identificador consultable; nunca se comprobó más allá del resumen. SIN TEXTO COMPLETO</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>(no hay texto completo: el artículo no se ha podido leer)</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Use of bacteriophages in the treatment of infected wounds in patients who have allergy to antibiotics</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H52"/>
+  <autoFilter ref="A1:H56"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/verificables revisión sistemática/S16_excluidos_tras_leer_el_texto_completo.xlsx
+++ b/verificables revisión sistemática/S16_excluidos_tras_leer_el_texto_completo.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$H$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Datos'!$A$1:$H$119</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -529,7 +529,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>55 filas de datos</t>
+          <t>118 filas de datos</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-06</t>
+          <t>Generado el 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H56"/>
+  <dimension ref="A1:H119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -3013,8 +3013,2654 @@
         </is>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>EST-005</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>NOPDF</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Artículo publicado cuyo texto completo no se obtuvo. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>(sin PDF del artículo completo)</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Successful adjunctive use of bacteriophage therapy for treatment of multidrug-resistant Pseudomonas aeruginosa infection in a cystic fibrosis patient.</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>EST-018</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>NOPDF</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Artículo publicado cuyo texto completo no se obtuvo. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>(sin PDF del artículo completo)</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Bacteriophage therapy in clinical practice: case studies of Pseudomonas aeruginosa infections.</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>EST-022</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>NOPDF</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>(sin PDF del artículo completo)</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Individual Patient Expanded Access for AB-PA01, an Investigational Anti-Pseudomonas Aeruginosa Bacteriophage Therapeutic</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>EST-023</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>NOPDF</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>(sin PDF del artículo completo)</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Bacteriophage Therapy TP-102 in Patients With Diabetic Foot Infection</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>EST-025</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>NOPDF</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>(sin PDF del artículo completo)</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Bacteriophage Therapy in Patients With Prosthetic Joint Infections</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>EST-026</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>NOPDF</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>(sin PDF del artículo completo)</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Bacteriophage Therapy in Patients With Prosthetic Joint Infections (PJI)</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>EST-028</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>NOPDF</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Artículo publicado cuyo texto completo no se obtuvo. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>(sin PDF del artículo completo)</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>A feasibility study for personalized phage therapy against drug-resistant bacteria in Japan.</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>EST-029</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>NOPDF</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Artículo publicado cuyo texto completo no se obtuvo. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>(sin PDF del artículo completo)</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Randomized double-blind study on safety and tolerability of TP-102 phage cocktail in patients with infected and non-infected diabetic foot ulcers.</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>EST-032</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>NOPDF</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Artículo publicado cuyo texto completo no se obtuvo. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>(sin PDF del artículo completo)</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Refractory Pseudomonas Bacteremia in a 2-Year-Old Sterilized by Bacteriophage Therapy.</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>EST-033</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>NOPDF</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Artículo publicado cuyo texto completo no se obtuvo. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>(sin PDF del artículo completo)</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Bacteriophage Therapy of Ventilator-associated Pneumonia and Empyema Caused by Pseudomonas aeruginosa.</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>EST-036</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>NOPDF</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>(sin PDF del artículo completo)</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>A Randomized Controlled Trial of Bacteriophage Cocktail Therapy for Multidrug-Resistant Gram-Negative Ventilator-Associated Pneumonia</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>EST-054</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>NOPDF</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Artículo publicado cuyo texto completo no se obtuvo. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>(sin PDF del artículo completo)</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Bacteriophage Therapy for Chronic Mastoiditis.</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>EST-056</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>NOPDF</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>(sin PDF del artículo completo)</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Bacteriophages in Addition to Antibiotics for the Treatment of Patients with Infective Endocarditis</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>EST-064</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>NOPDF</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Artículo publicado cuyo texto completo no se obtuvo. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>(sin PDF del artículo completo)</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Adjunctive bacteriophage therapy for refractory/resistant Pseudomonas aeruginosa infections: Bottlenecks and proposed solutions.</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>EST-065</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>NOPDF</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Artículo publicado cuyo texto completo no se obtuvo. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>(sin PDF del artículo completo)</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Successful phage therapy in a patient with prosthetic joint infection; [Tratamiento exitoso con fagoterapia en una paciente con infección periprotésica]</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>EST-066</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>NOPDF</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>(sin PDF del artículo completo)</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Phage Therapy for the Prevention and Treatment of Wound Infections in Burned Patients</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>EST-068</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>NOPDF</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>(sin PDF del artículo completo)</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>A three part randomized, double-blind, placebo-controlled, parallel group SAD and MD clinical study to evaluate the safety, tolerability and preliminary efficacy of an inhaled (nebulized) phage cocktail in healthy subjects and in patients with chronic colonization of the lung with Pseudomonas aeruginosa</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>EST-069</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>NOPDF</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>(sin PDF del artículo completo)</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>A two part, randomized, double-blind, placebo-controlled, parallel group SAD and MD clinical study to evaluate the safety, tolerability and preliminary efficacy of an inhaled (nebulized) phage cocktail in healthy subjects and in patients with chronic colonization of the lung with Pseudomonas aeruginosa</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>EST-071</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>NOPDF</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>(sin PDF del artículo completo)</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Investigating phage therapy in the prevention of ventilator-induced bacterial pneumonia in patients admitted to the pediatric intensive care unit</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>EST-073</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>NOPDF</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Artículo publicado cuyo texto completo no se obtuvo. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>(sin PDF del artículo completo)</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Bacteriophage Therapy of Chronic Nonhealing Wound: Clinical Study.</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>EST-078</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>NOPDF</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Solo existe como resumen de congreso. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>(sin PDF del artículo completo)</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Efficacy of Bacteriophage Therapy in the Treatment of Diabetic Foot Ulcers: a Pilot Study from South India</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>EST-081</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>NOPDF</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Artículo publicado cuyo texto completo no se obtuvo. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>(sin PDF del artículo completo)</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Bacteriophage therapy as a treatment option for transplant infections.</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>EST-082</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>NOPDF</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>(sin PDF del artículo completo)</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Ph 1/2 Study Evaluating Safety and Tolerability of Inhaled AP-PA02 in Subjects With Chronic Pseudomonas Aeruginosa Lung Infections and Cystic Fibrosis</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>EST-084</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>NOPDF</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>(sin PDF del artículo completo)</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Study to Evaluate the Safety, Phage Kinetics, and Efficacy of Inhaled AP-PA02 in Subjects With Non-Cystic Fibrosis Bronchiectasis and Chronic Pulmonary Pseudomonas Aeruginosa Infection</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>EST-097</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>NOPDF</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>(sin PDF del artículo completo)</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Phage Therapy for the Prevention and Treatment of Pressure Ulcers.</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>EST-098</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>NOPDF</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Artículo publicado cuyo texto completo no se obtuvo. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>(sin PDF del artículo completo)</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Bacteriophage therapy as a treatment option for complex cardiovascular implant infection: The German Heart Center Berlin experience.</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>EST-099</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>NOPDF</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>(sin PDF del artículo completo)</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Evaluation of safety and effectiveness of a nebulised phage cocktail in patients with chronic rhinosinusitis (CRS)</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>EST-102</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>NOPDF</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>(sin PDF del artículo completo)</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>A randomized, double-blind clinical trial of phage nebulized inhalation for the treatment of respiratory tract infections caused by multi-drug resistant Pseudomonas aeruginosa</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>EST-104</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>NOPDF</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>(sin PDF del artículo completo)</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Bacteriophage Clinical Trial for Periprosthetic Joint Infection of Multidrug Resistant Pseudomonas Aeruginosa</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>EST-107</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>NOPDF</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>(sin PDF del artículo completo)</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Bacteriophage Therapy in First Time Chronic Prosthetic Joint Infections</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>EST-110</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>NOPDF</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Artículo publicado cuyo texto completo no se obtuvo. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>(sin PDF del artículo completo)</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Successful Use of Phage and Antibiotics Therapy for the Eradication of Two Bacterial Pathogens from the Respiratory Tract of an Infant.</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>EST-111</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>NOPDF</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>(sin PDF del artículo completo)</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Bacteriophage Cocktail Therapy for Multidrug-Resistant Gram-Negative Ventilator-Associated Pneumonia</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>EST-112</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>NOPDF</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>(sin PDF del artículo completo)</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Safety of Combined Intravenous Antibiotic and Bacteriophage Therapy in Adults With Cystic Fibrosis and Antibiotic-Resistant Lung Infections</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>EST-113</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>NOPDF</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>(sin PDF del artículo completo)</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Randomized Controlled Study on the Safety and Efficacy of Phage Cocktail in the Treatment of Multidrug-Resistant Bacterial Skin Infections</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>EST-114</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>NOPDF</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>(sin PDF del artículo completo)</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Personalized Phage Treatment in Covid-19 Patients With Bacterial Co-Infections Microbials for Pneumonia or Bacteremia/Septicemia</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>EST-115</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>NOPDF</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Artículo publicado cuyo texto completo no se obtuvo. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>(sin PDF del artículo completo)</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Antiphage activity of sera during phage therapy in relation to its outcome.</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>EST-119</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>NOPDF</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>(sin PDF del artículo completo)</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Phage therapy for prevention of secondary bacterial pneumonia in COVID-19</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>EST-133</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>NOPDF</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Solo existe como resumen de congreso. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>(sin PDF del artículo completo)</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Phage therapy for the treatment for urinary tract infection: results of in-vitro screenings and in-vivo application using commercially available bacteriophage cocktails</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>EST-137</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>NOPDF</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>(sin PDF del artículo completo)</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>"Debridement PhagE AnTibiotics for PJI"</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>EST-140</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>NOPDF</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Artículo publicado cuyo texto completo no se obtuvo. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>(sin PDF del artículo completo)</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Novel bacteriophage therapy for treatment of left ventricular assist device infection.</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>EST-143</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>NOPDF</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>(sin PDF del artículo completo)</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Chronic non healing ulcer and bacteriophage therapy</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>EST-149</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>NOPDF</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>(sin PDF del artículo completo)</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Study to phages for prevention and treatment of difficult-to-treat resistant Pseudomonas aeruginosa infection</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>EST-153</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>NOPDF</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>(sin PDF del artículo completo)</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Evaluation of Safety and Efficacy of Phage Therapy for Drug-resistant Bacterial Infections: An Exploratory, Prospective Single-arm Study</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>EST-154</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>NOPDF</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>(sin PDF del artículo completo)</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Phase 1/2a to Assess the Safety and Tolerability of TP-122A for the Treatment of Ventilator-Associated Pneumonia</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>EST-155</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>NOPDF</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>(sin PDF del artículo completo)</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Efficacy and safety of bacteriophage in treating severe drug-resistant lower respiratory tract infections in children: a randomized controlled trial</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>EST-156</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>NOPDF</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>(sin PDF del artículo completo)</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Phase 2b Randomized, Double-Blind Study with Phage for CF Subjects with Pseudomonas Lung Infection</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>EST-157</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>NOPDF</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Artículo publicado cuyo texto completo no se obtuvo. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>(sin PDF del artículo completo)</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>A Randomized, Placebo-controlled, Double-blind Clinical Trial of Bacteriophage Cocktails in Chronic Wound Infections.</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>EST-158</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>NOPDF</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>(sin PDF del artículo completo)</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Bacteriophage Effects on Pseudomonas Aeruginosa</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>EST-160</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>NOPDF</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>(sin PDF del artículo completo)</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>A Randomized Controlled Trial on the Safety and Efficacy of Phage Cocktail Therapy for Multidrug-Resistant Bacterial Skin Infections</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>EST-161</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>NOPDF</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>(sin PDF del artículo completo)</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>MP101 in Adults With Acute Pseudomonas Aeruginosa Pneumonia</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>EST-162</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>NOPDF</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>(sin PDF del artículo completo)</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Phase 1 Study of MP101 in Adults With Acute Pseudomonas aeruginosa Pneumonia</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>EST-165</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>NOPDF</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Artículo publicado cuyo texto completo no se obtuvo. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>(sin PDF del artículo completo)</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Use of Customized Bacteriophages in the Treatment of Chronic Nonhealing Wounds: A Prospective Study.</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>EST-167</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>NOPDF</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Artículo publicado cuyo texto completo no se obtuvo. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>(sin PDF del artículo completo)</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Biological Therapy on Infected Traumatic Wounds: A Case-Control Study.</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>EST-171</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>NOPDF</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>(sin PDF del artículo completo)</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Yiqi Huoxue Jiedu Formula Combined With Bacteriophages in the Treatment of Severe Pneumonia</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>EST-172</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>NOPDF</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>(sin PDF del artículo completo)</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Study to assess the Safety and Efficacy of Bacteriophage in the treatment of Diabetic foot infection</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>EST-186</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>NOPDF</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>(sin PDF del artículo completo)</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Phage4Cure-001 - A three part randomized, double-blind, placebo-controlled, parallel group SAD and MD clinical study to evaluate the safety, tolerability and preliminary efficacy o</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>EST-188</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>NOPDF</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Solo existe como resumen de congreso. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>(sin PDF del artículo completo)</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Potential treatment method of recurrent urinary tract infection in postmenopausal kidney transplant recipients: the results of pilot study</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>EST-190</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>NOPDF</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>(sin PDF del artículo completo)</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Phage-Antibiotic Combination Therapy for Multidrug-Resistant Infections: a Prospective Study</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>EST-191</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>NOPDF</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>(sin PDF del artículo completo)</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>BMX-04-002 - A Phase 2b, Randomized, Double-Blind, Placebo-Controlled, Multicenter Study to Evaluate Nebulized Bacteriophage Treatment in Outpatient Adult Cystic Fibrosis (CF) Subj</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>EST-201</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>NOPDF</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>(sin PDF del artículo completo)</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Study With Phage for CF Subjects With Pseudomonas Lung Infection</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>EST-202</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>NOPDF</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>(sin PDF del artículo completo)</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>The effect of Bacteriophage on Diabetic foot Ulcers</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>EST-215</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>NOPDF</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>(sin PDF del artículo completo)</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Clinical Trial to Demonstrate the Safety and Efficacy of DUOFAG®</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>EST-217</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>NOPDF</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Sin PDF del articulo completo con acceso: el texto no se obtuvo, o el estudio solo existe como resumen de congreso o ficha de registro</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Solo existe como ficha de registro de ensayo, sin artículo publicado. Criterio: solo estudios con el PDF del artículo completo accesible (ampliación de NOREC firmada el 2026-10-06).</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>(sin PDF del artículo completo)</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Evaluate the effect of bacteriophage in pressure ulcers</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>D. Valdiviezo y N. Trelles</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H56"/>
+  <autoFilter ref="A1:H119"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/verificables revisión sistemática/S16_excluidos_tras_leer_el_texto_completo.xlsx
+++ b/verificables revisión sistemática/S16_excluidos_tras_leer_el_texto_completo.xlsx
@@ -649,7 +649,7 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-07</t>
+          <t>Generado el 2026-10-08</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S16_excluidos_tras_leer_el_texto_completo.xlsx
+++ b/verificables revisión sistemática/S16_excluidos_tras_leer_el_texto_completo.xlsx
@@ -649,7 +649,7 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-08</t>
+          <t>Generado el 2026-10-12</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S16_excluidos_tras_leer_el_texto_completo.xlsx
+++ b/verificables revisión sistemática/S16_excluidos_tras_leer_el_texto_completo.xlsx
@@ -649,7 +649,7 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-12</t>
+          <t>Generado el 2026-10-14</t>
         </is>
       </c>
     </row>

--- a/verificables revisión sistemática/S16_excluidos_tras_leer_el_texto_completo.xlsx
+++ b/verificables revisión sistemática/S16_excluidos_tras_leer_el_texto_completo.xlsx
@@ -649,7 +649,7 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>Generado el 2026-10-14</t>
+          <t>Generado el 2026-10-15</t>
         </is>
       </c>
     </row>
